--- a/public/exports-from-60/29189730.xlsx
+++ b/public/exports-from-60/29189730.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256418</t>
+          <t xml:space="preserve">311256422</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654759</t>
+          <t xml:space="preserve">311654760</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -13039,7 +13039,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706715</t>
+          <t xml:space="preserve">311706717</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13339,7 +13339,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706728</t>
+          <t xml:space="preserve">311706741</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706728</t>
+          <t xml:space="preserve">311706741</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706728</t>
+          <t xml:space="preserve">311706741</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13864,7 +13864,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706895</t>
+          <t xml:space="preserve">311706919</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706895</t>
+          <t xml:space="preserve">311706919</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -16339,12 +16339,12 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710301</t>
+          <t xml:space="preserve">311710302</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M218" t="inlineStr">
@@ -16564,12 +16564,12 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710293</t>
+          <t xml:space="preserve">311710302</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M221" t="inlineStr">

--- a/public/exports-from-60/29189730.xlsx
+++ b/public/exports-from-60/29189730.xlsx
@@ -6214,7 +6214,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256422</t>
+          <t xml:space="preserve">311256418</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -12364,12 +12364,12 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706451</t>
+          <t xml:space="preserve">311706452</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -12439,12 +12439,12 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706451</t>
+          <t xml:space="preserve">311706452</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -12514,12 +12514,12 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706451</t>
+          <t xml:space="preserve">311706452</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -12589,12 +12589,12 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706451</t>
+          <t xml:space="preserve">311706452</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706451</t>
+          <t xml:space="preserve">311706452</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -13039,7 +13039,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706717</t>
+          <t xml:space="preserve">311706715</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13339,7 +13339,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706741</t>
+          <t xml:space="preserve">311706979</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706741</t>
+          <t xml:space="preserve">311706979</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706741</t>
+          <t xml:space="preserve">311706979</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13864,7 +13864,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706919</t>
+          <t xml:space="preserve">311706982</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706919</t>
+          <t xml:space="preserve">311706982</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -14089,7 +14089,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706709</t>
+          <t xml:space="preserve">311706968</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14164,7 +14164,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706709</t>
+          <t xml:space="preserve">311706968</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -16264,12 +16264,12 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710302</t>
+          <t xml:space="preserve">311710303</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
@@ -16339,12 +16339,12 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710302</t>
+          <t xml:space="preserve">311710301</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710302</t>
+          <t xml:space="preserve">311710304</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -16489,12 +16489,12 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710302</t>
+          <t xml:space="preserve">311710306</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
@@ -16564,12 +16564,12 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710302</t>
+          <t xml:space="preserve">311710293</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">

--- a/public/exports-from-60/29189730.xlsx
+++ b/public/exports-from-60/29189730.xlsx
@@ -8089,7 +8089,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654760</t>
+          <t xml:space="preserve">311654759</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -12364,12 +12364,12 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706452</t>
+          <t xml:space="preserve">311706451</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -12439,12 +12439,12 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706452</t>
+          <t xml:space="preserve">311706451</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -12514,12 +12514,12 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706452</t>
+          <t xml:space="preserve">311706451</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -12589,12 +12589,12 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706452</t>
+          <t xml:space="preserve">311706451</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706452</t>
+          <t xml:space="preserve">311706451</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -13339,7 +13339,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706979</t>
+          <t xml:space="preserve">311706728</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706979</t>
+          <t xml:space="preserve">311706728</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706979</t>
+          <t xml:space="preserve">311706728</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13864,7 +13864,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706982</t>
+          <t xml:space="preserve">311706895</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706982</t>
+          <t xml:space="preserve">311706895</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -14089,7 +14089,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706968</t>
+          <t xml:space="preserve">311706709</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14164,7 +14164,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706968</t>
+          <t xml:space="preserve">311706709</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -16264,12 +16264,12 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710303</t>
+          <t xml:space="preserve">311710302</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M217" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710304</t>
+          <t xml:space="preserve">311710302</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -16489,12 +16489,12 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710306</t>
+          <t xml:space="preserve">311710302</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M220" t="inlineStr">
